--- a/VCR TEMPLATE.xlsx
+++ b/VCR TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BE247B-75E4-44D1-90E1-32E91704CA46}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA41DE9B-CE8B-4AB0-B8A7-1ABF9A5B7EBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{F8A25437-9139-478F-93E2-108375DD4A5D}"/>
   </bookViews>
@@ -79,12 +79,6 @@
     <t>FORM PENGAJUAN VOUCHER BIG SALES</t>
   </si>
   <si>
-    <t>TELE/KAM</t>
-  </si>
-  <si>
-    <t>SGM/MOD</t>
-  </si>
-  <si>
     <t>ALC</t>
   </si>
   <si>
@@ -95,6 +89,12 @@
   </si>
   <si>
     <t>SUNARTO</t>
+  </si>
+  <si>
+    <t>SGM / MOD</t>
+  </si>
+  <si>
+    <t>TELE / KAM</t>
   </si>
 </sst>
 </file>
@@ -248,6 +248,18 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -257,23 +269,11 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,10 +845,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="16" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="17" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.140625" style="16" bestFit="1" customWidth="1"/>
@@ -879,23 +879,23 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
     </row>
     <row r="3" spans="1:15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
@@ -924,21 +924,21 @@
       <c r="G4" s="20"/>
       <c r="H4" s="15"/>
       <c r="I4" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="29"/>
+      <c r="L4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="M4" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="32"/>
-      <c r="L4" s="27" t="s">
+      <c r="N4" s="29"/>
+      <c r="O4" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="32"/>
-      <c r="O4" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -950,13 +950,13 @@
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
     </row>
     <row r="6" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -967,13 +967,13 @@
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
     </row>
     <row r="7" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
@@ -984,13 +984,13 @@
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
       <c r="H7" s="15"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
     </row>
     <row r="8" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
@@ -1001,13 +1001,13 @@
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
     </row>
     <row r="9" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
@@ -1019,13 +1019,13 @@
       <c r="G9" s="20"/>
       <c r="H9" s="15"/>
       <c r="I9" s="21"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
       <c r="L9" s="27"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
       <c r="O9" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1062,81 +1062,75 @@
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="35" t="s">
+      <c r="I12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34" t="s">
+      <c r="K12" s="30"/>
+      <c r="L12" s="30" t="s">
         <v>12</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N12" s="28"/>
-      <c r="O12" s="33" t="s">
+      <c r="O12" s="36" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="34"/>
+      <c r="L13" s="30"/>
       <c r="M13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="N13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O13" s="33"/>
+      <c r="O13" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O5:O8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:K8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="M5:N8"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
@@ -1153,6 +1147,12 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
+    <mergeCell ref="O5:O8"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:K8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="M5:N8"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="57" orientation="landscape" r:id="rId1"/>

--- a/VCR TEMPLATE.xlsx
+++ b/VCR TEMPLATE.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA41DE9B-CE8B-4AB0-B8A7-1ABF9A5B7EBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680B8D74-CE47-4ED3-A663-B6547017FE2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{F8A25437-9139-478F-93E2-108375DD4A5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -248,32 +247,32 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -290,255 +289,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>930</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Rute Transjakarta 7E Kampung Rambutan-Pasar Minggu">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2FB06C-9527-4F59-9351-90CD7500A0A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1" y="0"/>
-          <a:ext cx="3658529" cy="9144000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Rute Koridor 7 TransJakarta">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9EC4EFF-A83B-4272-A70A-E57BE9E3FFE4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4267200" y="0"/>
-          <a:ext cx="3600450" cy="9144000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="Rute Koridor 9 Transjakarta: Penghubung Utara dan Timur Jakarta">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18CAFFC0-C7FC-4CAC-9E62-914B171287E1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8534400" y="0"/>
-          <a:ext cx="3600450" cy="5715000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="Rute 13B Transjakarta, Tarif &amp; Jam Operasional">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C49A82CB-6ECB-413B-A977-F8AC717ABB40}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="12801600" y="0"/>
-          <a:ext cx="3829050" cy="9753600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -879,23 +629,23 @@
       <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
     </row>
     <row r="3" spans="1:15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
@@ -926,17 +676,17 @@
       <c r="I4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="29"/>
+      <c r="K4" s="32"/>
       <c r="L4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="29"/>
+      <c r="N4" s="32"/>
       <c r="O4" s="13" t="s">
         <v>19</v>
       </c>
@@ -950,13 +700,13 @@
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
     </row>
     <row r="6" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
@@ -967,13 +717,13 @@
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
     </row>
     <row r="7" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
@@ -984,13 +734,13 @@
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
       <c r="H7" s="15"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
     </row>
     <row r="8" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
@@ -1001,13 +751,13 @@
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
     </row>
     <row r="9" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
@@ -1019,11 +769,11 @@
       <c r="G9" s="20"/>
       <c r="H9" s="15"/>
       <c r="I9" s="21"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
       <c r="L9" s="27"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
       <c r="O9" s="13" t="s">
         <v>20</v>
       </c>
@@ -1062,75 +812,81 @@
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="37" t="s">
+      <c r="I12" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30" t="s">
+      <c r="K12" s="34"/>
+      <c r="L12" s="34" t="s">
         <v>12</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="N12" s="28"/>
-      <c r="O12" s="36" t="s">
+      <c r="O12" s="33" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="30"/>
+      <c r="L13" s="34"/>
       <c r="M13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="N13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O13" s="36"/>
+      <c r="O13" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="O5:O8"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:K8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="M5:N8"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
@@ -1147,24 +903,8 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="O5:O8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:K8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="M5:N8"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="57" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{144DB874-9215-45C2-8359-62DD0068FD91}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/VCR TEMPLATE.xlsx
+++ b/VCR TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680B8D74-CE47-4ED3-A663-B6547017FE2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBF31827-8B74-42DD-B8C8-747597C26222}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{F8A25437-9139-478F-93E2-108375DD4A5D}"/>
   </bookViews>
@@ -142,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -165,6 +165,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -185,9 +211,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -244,8 +267,17 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -255,24 +287,18 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,19 +621,19 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="16" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" style="17" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="16" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="16" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" style="16" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="25" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="15" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="24" customWidth="1"/>
     <col min="12" max="12" width="19.28515625" style="2" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" style="25" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" style="24" customWidth="1"/>
     <col min="15" max="15" width="19.28515625" style="4" customWidth="1"/>
     <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -616,221 +642,221 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="18"/>
+      <c r="E1" s="17"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="26"/>
+      <c r="K1" s="25"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="26"/>
+      <c r="N1" s="25"/>
       <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
     </row>
     <row r="3" spans="1:15" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="10"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="21" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="32"/>
-      <c r="L4" s="27" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="32"/>
-      <c r="O4" s="13" t="s">
+      <c r="N4" s="27"/>
+      <c r="O4" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-    </row>
-    <row r="6" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-    </row>
-    <row r="7" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-    </row>
-    <row r="8" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
-    </row>
-    <row r="9" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="13" t="s">
+    <row r="5" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+    </row>
+    <row r="6" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+    </row>
+    <row r="7" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+    </row>
+    <row r="8" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+    </row>
+    <row r="9" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="11"/>
+    <row r="10" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="18"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="26"/>
+      <c r="K11" s="25"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="26"/>
+      <c r="N11" s="25"/>
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="33" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="28" t="s">
         <v>6</v>
       </c>
       <c r="H12" s="35" t="s">
@@ -839,54 +865,48 @@
       <c r="I12" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34" t="s">
+      <c r="K12" s="28"/>
+      <c r="L12" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="N12" s="28"/>
-      <c r="O12" s="33" t="s">
+      <c r="N12" s="37"/>
+      <c r="O12" s="34" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
       <c r="E13" s="35"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="34"/>
-      <c r="M13" s="9" t="s">
+      <c r="L13" s="28"/>
+      <c r="M13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="O13" s="33"/>
+      <c r="O13" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="O5:O8"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:K8"/>
-    <mergeCell ref="L5:L8"/>
-    <mergeCell ref="M5:N8"/>
+  <mergeCells count="23">
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
@@ -903,6 +923,13 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
+    <mergeCell ref="O5:O8"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:K8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="M5:N8"/>
+    <mergeCell ref="M12:N12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="57" orientation="landscape" r:id="rId1"/>
